--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7FEB2C-B6E6-429F-B12F-3B65E28837A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ACE384-5EE1-44B4-AEC0-731BF8F36769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="1" shapeId="0" xr:uid="{C865023D-FBB7-478B-9309-6C469B143875}">
+    <comment ref="G4" authorId="1" shapeId="0" xr:uid="{C865023D-FBB7-478B-9309-6C469B143875}">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="270">
   <si>
     <t>Id</t>
   </si>
@@ -811,6 +811,135 @@
   </si>
   <si>
     <t>20005003,20005001</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChapterName_EN</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greenwood Town</t>
+  </si>
+  <si>
+    <t>Level 1 of the Mine Shaft</t>
+  </si>
+  <si>
+    <t>Second floor of the mine</t>
+  </si>
+  <si>
+    <t>Outside the Forest</t>
+  </si>
+  <si>
+    <t>Deep in the Forest</t>
+  </si>
+  <si>
+    <t>Underground Cavern</t>
+  </si>
+  <si>
+    <t>The first floor of the stone tomb</t>
+  </si>
+  <si>
+    <t>Second Floor of the Tomb</t>
+  </si>
+  <si>
+    <t>Desert of Scorching Heat</t>
+  </si>
+  <si>
+    <t>Oasis Path</t>
+  </si>
+  <si>
+    <t>Forget the Ruins</t>
+  </si>
+  <si>
+    <t>Floor 1 of the Dungeon</t>
+  </si>
+  <si>
+    <t>Second floor of the dungeon</t>
+  </si>
+  <si>
+    <t>Frozen Town</t>
+  </si>
+  <si>
+    <t>Frozen Forest</t>
+  </si>
+  <si>
+    <t>Frozen Fortress</t>
+  </si>
+  <si>
+    <t>Thousand-needle forest</t>
+  </si>
+  <si>
+    <t>Frozen Path</t>
+  </si>
+  <si>
+    <t>Frozen Demon穴</t>
+  </si>
+  <si>
+    <t>Dusk Town</t>
+  </si>
+  <si>
+    <t>The dusk outskirts</t>
+  </si>
+  <si>
+    <t>Dusk Forest</t>
+  </si>
+  <si>
+    <t>Dusk Mine Level 1</t>
+  </si>
+  <si>
+    <t>Second floor of the Twilight Mine</t>
+  </si>
+  <si>
+    <t>Crack Stone Canyon</t>
+  </si>
+  <si>
+    <t>Hell Rift Valley</t>
+  </si>
+  <si>
+    <t>Dark Town</t>
+  </si>
+  <si>
+    <t>Strange path</t>
+  </si>
+  <si>
+    <t>Corrosive Land</t>
+  </si>
+  <si>
+    <t>The first floor of the Dark Corridor</t>
+  </si>
+  <si>
+    <t>Dark Corridor Level 2</t>
+  </si>
+  <si>
+    <t>Dark Corridor, 3rd floor</t>
+  </si>
+  <si>
+    <t>Heart of Darkness</t>
+  </si>
+  <si>
+    <t>Skyland</t>
+  </si>
+  <si>
+    <t>Clear Sky Camp</t>
+  </si>
+  <si>
+    <t>Azure Sky Cavern</t>
+  </si>
+  <si>
+    <t>Mysterious Door - Joy</t>
+  </si>
+  <si>
+    <t>Mysterious Door</t>
+  </si>
+  <si>
+    <t>In the eyes of people, this area is deeply dangerous. Dear adventurer, are you ready to start your expedition?</t>
+  </si>
+  <si>
+    <t>ChapterDes_EN</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1013,7 +1142,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1079,13 +1208,63 @@
     <xf numFmtId="49" fontId="1" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1170,13 +1349,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C4:H5" totalsRowShown="0">
-  <autoFilter ref="C4:H5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C4:I5" totalsRowShown="0">
+  <autoFilter ref="C4:I5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ChapterName"/>
+    <tableColumn id="7" xr3:uid="{BF7A43A1-7952-4509-B9DC-1DC3D8F11E4C}" name="ChapterName_EN" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Music"/>
-    <tableColumn id="6" xr3:uid="{F00E6764-AD8C-429D-A124-148C7791A5DF}" name="MapType" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{F00E6764-AD8C-429D-A124-148C7791A5DF}" name="MapType" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="EnterLv"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="BossIcon"/>
   </tableColumns>
@@ -1471,22 +1651,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:S53"/>
+  <dimension ref="C1:U53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="6" width="16.75" customWidth="1"/>
-    <col min="7" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="11" width="17.25" customWidth="1"/>
-    <col min="12" max="13" width="26.625" customWidth="1"/>
-    <col min="14" max="14" width="73.375" customWidth="1"/>
-    <col min="15" max="15" width="87" customWidth="1"/>
-    <col min="16" max="16" width="63.25" customWidth="1"/>
-    <col min="17" max="19" width="23.125" customWidth="1"/>
+    <col min="4" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="9" width="17.25" customWidth="1"/>
+    <col min="10" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="13" width="17.25" customWidth="1"/>
+    <col min="14" max="15" width="26.625" customWidth="1"/>
+    <col min="16" max="16" width="73.375" customWidth="1"/>
+    <col min="17" max="17" width="87" customWidth="1"/>
+    <col min="18" max="18" width="63.25" customWidth="1"/>
+    <col min="19" max="21" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K2" s="26" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1494,105 +1680,117 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="S3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="4" t="s">
         <v>27</v>
       </c>
@@ -1603,31 +1801,31 @@
         <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>29</v>
@@ -1636,2085 +1834,2349 @@
         <v>28</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>10001</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="9">
         <v>70001910</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="6">
+      <c r="J6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L6" s="6">
         <v>10001</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="O6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="P6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="18" t="s">
+      <c r="Q6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="18" t="s">
+      <c r="R6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="S6" s="6">
         <v>10001</v>
       </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6">
+      <c r="T6" s="6"/>
+      <c r="U6" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="6">
         <v>10002</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G7" s="10">
+      <c r="H7" s="10">
         <v>3</v>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="9">
         <v>70001920</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="J7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L7" s="6">
         <v>10002</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="M7" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="O7" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="P7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="Q7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="R7" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="S7" s="6">
         <v>10002</v>
       </c>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6">
+      <c r="T7" s="6"/>
+      <c r="U7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>10003</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="G8" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="7">
         <v>5</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="9">
         <v>70001930</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="6">
+      <c r="J8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L8" s="6">
         <v>10003</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="M8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="9">
+      <c r="O8" s="9">
         <v>1010</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="P8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="O8" s="18" t="s">
+      <c r="Q8" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="18" t="s">
+      <c r="R8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="S8" s="6">
         <v>10003</v>
       </c>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6">
+      <c r="T8" s="6"/>
+      <c r="U8" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="6">
         <v>10004</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="G9" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="7">
         <v>6</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <v>70001940</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="J9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L9" s="6">
         <v>10004</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="M9" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="O9" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="P9" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="Q9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="R9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="S9" s="6">
         <v>10004</v>
       </c>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6">
+      <c r="T9" s="6"/>
+      <c r="U9" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="6">
         <v>10005</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="G10" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="7">
         <v>6</v>
       </c>
-      <c r="H10" s="9">
+      <c r="I10" s="9">
         <v>70001950</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="J10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L10" s="6">
         <v>10005</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="M10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="9">
+      <c r="O10" s="9">
         <v>1011</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="P10" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="O10" s="18" t="s">
+      <c r="Q10" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="18" t="s">
+      <c r="R10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="S10" s="6">
         <v>10005</v>
       </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6">
+      <c r="T10" s="6"/>
+      <c r="U10" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="6">
         <v>10006</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="G11" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G11" s="7">
+      <c r="H11" s="7">
         <v>12</v>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <v>70001960</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="J11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L11" s="6">
         <v>10006</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="M11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="9">
+      <c r="O11" s="9">
         <v>1012</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="P11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="O11" s="18" t="s">
+      <c r="Q11" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="P11" s="18" t="s">
+      <c r="R11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="S11" s="6">
         <v>10006</v>
       </c>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6">
+      <c r="T11" s="6"/>
+      <c r="U11" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="6">
         <v>10007</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="G12" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G12" s="7">
+      <c r="H12" s="7">
         <v>8</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>70001970</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="6">
+      <c r="J12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L12" s="6">
         <v>10007</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="M12" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="O12" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="P12" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="O12" s="18" t="s">
+      <c r="Q12" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="P12" s="18" t="s">
+      <c r="R12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="S12" s="6">
         <v>10007</v>
       </c>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6">
+      <c r="T12" s="6"/>
+      <c r="U12" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="6">
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="G13" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G13" s="7">
+      <c r="H13" s="7">
         <v>8</v>
       </c>
-      <c r="H13" s="9">
+      <c r="I13" s="9">
         <v>70002910</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="6">
+      <c r="J13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L13" s="6">
         <v>10008</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="M13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="O13" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="P13" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="O13" s="18" t="s">
+      <c r="Q13" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="P13" s="18" t="s">
+      <c r="R13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="S13" s="6">
         <v>10008</v>
       </c>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6">
+      <c r="T13" s="6"/>
+      <c r="U13" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
         <v>20001</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="G14" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G14" s="9">
+      <c r="H14" s="9">
         <v>15</v>
       </c>
-      <c r="H14" s="9">
+      <c r="I14" s="9">
         <v>70002920</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="6">
+      <c r="J14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L14" s="6">
         <v>20001</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="M14" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="O14" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="P14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="Q14" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="P14" s="18" t="s">
+      <c r="R14" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="S14" s="6">
         <v>20001</v>
       </c>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6">
+      <c r="T14" s="6"/>
+      <c r="U14" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
         <v>20002</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="G15" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G15" s="9">
+      <c r="H15" s="9">
         <v>20</v>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="9">
         <v>70002920</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="6">
+      <c r="J15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L15" s="6">
         <v>20002</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="M15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="O15" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="P15" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="O15" s="18" t="s">
+      <c r="Q15" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="R15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="S15" s="6">
         <v>20002</v>
       </c>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6">
+      <c r="T15" s="6"/>
+      <c r="U15" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
         <v>20003</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="G16" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G16" s="9">
+      <c r="H16" s="9">
         <v>23</v>
       </c>
-      <c r="H16" s="9">
+      <c r="I16" s="9">
         <v>70002930</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="6">
+      <c r="J16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L16" s="6">
         <v>20003</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="M16" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="N16" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M16" s="9">
+      <c r="O16" s="9">
         <v>2012</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="P16" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="O16" s="18" t="s">
+      <c r="Q16" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="P16" s="18" t="s">
+      <c r="R16" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="S16" s="6">
         <v>20003</v>
       </c>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6">
+      <c r="T16" s="6"/>
+      <c r="U16" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
         <v>20004</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="G17" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G17" s="9">
+      <c r="H17" s="9">
         <v>25</v>
       </c>
-      <c r="H17" s="9">
+      <c r="I17" s="9">
         <v>70002940</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="6">
+      <c r="J17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L17" s="6">
         <v>20004</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="M17" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="O17" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="P17" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="O17" s="18" t="s">
+      <c r="Q17" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="P17" s="18" t="s">
+      <c r="R17" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="S17" s="6">
         <v>20004</v>
       </c>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6">
+      <c r="T17" s="6"/>
+      <c r="U17" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
         <v>20005</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="G18" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G18" s="9">
+      <c r="H18" s="9">
         <v>27</v>
       </c>
-      <c r="H18" s="9">
+      <c r="I18" s="9">
         <v>70002950</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="6">
+      <c r="J18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L18" s="6">
         <v>20005</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="M18" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="N18" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="M18" s="9">
+      <c r="O18" s="9">
         <v>2014</v>
       </c>
-      <c r="N18" s="12"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="18" t="s">
+      <c r="P18" s="12"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="S18" s="6">
         <v>20005</v>
       </c>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6">
+      <c r="T18" s="6"/>
+      <c r="U18" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
         <v>30001</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="G19" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G19" s="9">
+      <c r="H19" s="9">
         <v>30</v>
       </c>
-      <c r="H19" s="9">
+      <c r="I19" s="9">
         <v>70003910</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="6">
+      <c r="J19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L19" s="6">
         <v>30001</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="M19" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="N19" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="M19" s="9">
+      <c r="O19" s="9">
         <v>3002</v>
       </c>
-      <c r="N19" s="12"/>
-      <c r="O19" s="18" t="s">
+      <c r="P19" s="12"/>
+      <c r="Q19" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="P19" s="18" t="s">
+      <c r="R19" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="S19" s="6">
         <v>30001</v>
       </c>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6">
+      <c r="T19" s="6"/>
+      <c r="U19" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
         <v>30002</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="G20" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G20" s="9">
+      <c r="H20" s="9">
         <v>30</v>
       </c>
-      <c r="H20" s="9">
+      <c r="I20" s="9">
         <v>70003920</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="6">
+      <c r="J20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L20" s="6">
         <v>30002</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="M20" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="O20" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="N20" s="12"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="18" t="s">
+      <c r="P20" s="12"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="S20" s="6">
         <v>30002</v>
       </c>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6">
+      <c r="T20" s="6"/>
+      <c r="U20" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="6">
         <v>30003</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="G21" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G21" s="9">
+      <c r="H21" s="9">
         <v>32</v>
       </c>
-      <c r="H21" s="9">
+      <c r="I21" s="9">
         <v>70003930</v>
       </c>
-      <c r="I21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="6">
+      <c r="J21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L21" s="6">
         <v>30003</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="M21" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="9">
+      <c r="O21" s="9">
         <v>3012</v>
       </c>
-      <c r="N21" s="12"/>
-      <c r="O21" s="18" t="s">
+      <c r="P21" s="12"/>
+      <c r="Q21" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="P21" s="18" t="s">
+      <c r="R21" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="S21" s="6">
         <v>30003</v>
       </c>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6">
+      <c r="T21" s="6"/>
+      <c r="U21" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="6">
         <v>30004</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="G22" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G22" s="9">
+      <c r="H22" s="9">
         <v>34</v>
       </c>
-      <c r="H22" s="9">
+      <c r="I22" s="9">
         <v>70003940</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="6">
+      <c r="J22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L22" s="6">
         <v>30004</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="M22" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="N22" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="O22" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="N22" s="12"/>
-      <c r="O22" s="18" t="s">
+      <c r="P22" s="12"/>
+      <c r="Q22" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="P22" s="18" t="s">
+      <c r="R22" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="S22" s="6">
         <v>30004</v>
       </c>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6">
+      <c r="T22" s="6"/>
+      <c r="U22" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="6">
         <v>30005</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="G23" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G23" s="9">
+      <c r="H23" s="9">
         <v>36</v>
       </c>
-      <c r="H23" s="9">
+      <c r="I23" s="9">
         <v>70003950</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="6">
+      <c r="J23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L23" s="6">
         <v>30005</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="M23" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="N23" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="O23" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="18" t="s">
+      <c r="P23" s="12"/>
+      <c r="Q23" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="P23" s="18" t="s">
+      <c r="R23" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="S23" s="6">
         <v>30005</v>
       </c>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6">
+      <c r="T23" s="6"/>
+      <c r="U23" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="6">
         <v>30006</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="G24" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G24" s="9">
+      <c r="H24" s="9">
         <v>38</v>
       </c>
-      <c r="H24" s="9">
+      <c r="I24" s="9">
         <v>70003950</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J24" s="6">
+      <c r="J24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L24" s="6">
         <v>30006</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="M24" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="N24" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="M24" s="9">
+      <c r="O24" s="9">
         <v>3015</v>
       </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="18" t="s">
+      <c r="P24" s="12"/>
+      <c r="Q24" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="P24" s="18" t="s">
+      <c r="R24" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="S24" s="6">
         <v>30006</v>
       </c>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6">
+      <c r="T24" s="6"/>
+      <c r="U24" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="6">
         <v>40001</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="G25" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G25" s="9">
+      <c r="H25" s="9">
         <v>40</v>
       </c>
-      <c r="H25" s="9">
+      <c r="I25" s="9">
         <v>70004910</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="6">
+      <c r="J25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L25" s="6">
         <v>40001</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="M25" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="N25" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="O25" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="18" t="s">
+      <c r="P25" s="12"/>
+      <c r="Q25" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="P25" s="18" t="s">
+      <c r="R25" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="S25" s="6">
         <v>40001</v>
       </c>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6">
+      <c r="T25" s="6"/>
+      <c r="U25" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="6">
         <v>40002</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="G26" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G26" s="9">
+      <c r="H26" s="9">
         <v>40</v>
       </c>
-      <c r="H26" s="9">
+      <c r="I26" s="9">
         <v>70004920</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="6">
+      <c r="J26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L26" s="6">
         <v>40002</v>
       </c>
-      <c r="K26" s="14" t="s">
+      <c r="M26" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="N26" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="M26" s="19" t="s">
+      <c r="O26" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="N26" s="15"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="18" t="s">
+      <c r="P26" s="15"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="S26" s="6">
         <v>40002</v>
       </c>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6">
+      <c r="T26" s="6"/>
+      <c r="U26" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="6">
         <v>40003</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="G27" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G27" s="9">
+      <c r="H27" s="9">
         <v>42</v>
       </c>
-      <c r="H27" s="9">
+      <c r="I27" s="9">
         <v>70004930</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="6">
+      <c r="J27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L27" s="6">
         <v>40003</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="M27" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="N27" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="O27" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="N27" s="15"/>
-      <c r="O27" s="18" t="s">
+      <c r="P27" s="15"/>
+      <c r="Q27" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="P27" s="18" t="s">
+      <c r="R27" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="S27" s="6">
         <v>40003</v>
       </c>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6">
+      <c r="T27" s="6"/>
+      <c r="U27" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="6">
         <v>40004</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="G28" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G28" s="9">
+      <c r="H28" s="9">
         <v>44</v>
       </c>
-      <c r="H28" s="9">
+      <c r="I28" s="9">
         <v>70004940</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="6">
+      <c r="J28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L28" s="6">
         <v>40004</v>
       </c>
-      <c r="K28" s="14" t="s">
+      <c r="M28" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="N28" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="M28" s="19" t="s">
+      <c r="O28" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="N28" s="15"/>
-      <c r="O28" s="18" t="s">
+      <c r="P28" s="15"/>
+      <c r="Q28" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="P28" s="18" t="s">
+      <c r="R28" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q28" s="6">
+      <c r="S28" s="6">
         <v>40004</v>
       </c>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6">
+      <c r="T28" s="6"/>
+      <c r="U28" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="6">
         <v>40005</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="G29" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G29" s="9">
+      <c r="H29" s="9">
         <v>44</v>
       </c>
-      <c r="H29" s="9">
+      <c r="I29" s="9">
         <v>70004950</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="6">
+      <c r="J29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L29" s="6">
         <v>40005</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="M29" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="N29" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="M29" s="9">
+      <c r="O29" s="9">
         <v>4014</v>
       </c>
-      <c r="N29" s="12"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="18" t="s">
+      <c r="P29" s="12"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q29" s="6">
+      <c r="S29" s="6">
         <v>40005</v>
       </c>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6">
+      <c r="T29" s="6"/>
+      <c r="U29" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="6">
         <v>40006</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="G30" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G30" s="9">
+      <c r="H30" s="9">
         <v>46</v>
       </c>
-      <c r="H30" s="9">
+      <c r="I30" s="9">
         <v>70004950</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="6">
+      <c r="J30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L30" s="6">
         <v>40006</v>
       </c>
-      <c r="K30" s="14" t="s">
+      <c r="M30" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="N30" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="O30" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="N30" s="12"/>
-      <c r="O30" s="18" t="s">
+      <c r="P30" s="12"/>
+      <c r="Q30" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="P30" s="18" t="s">
+      <c r="R30" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q30" s="6">
+      <c r="S30" s="6">
         <v>40006</v>
       </c>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6">
+      <c r="T30" s="6"/>
+      <c r="U30" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="6">
         <v>40007</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="G31" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G31" s="9">
+      <c r="H31" s="9">
         <v>48</v>
       </c>
-      <c r="H31" s="9">
+      <c r="I31" s="9">
         <v>70004950</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J31" s="6">
+      <c r="J31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L31" s="6">
         <v>40007</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="M31" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="N31" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="M31" s="9">
+      <c r="O31" s="9">
         <v>4015</v>
       </c>
-      <c r="N31" s="12"/>
-      <c r="O31" s="18" t="s">
+      <c r="P31" s="12"/>
+      <c r="Q31" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="P31" s="18" t="s">
+      <c r="R31" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q31" s="6">
+      <c r="S31" s="6">
         <v>40007</v>
       </c>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6">
+      <c r="T31" s="6"/>
+      <c r="U31" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="6">
         <v>50001</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="G32" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G32" s="9">
+      <c r="H32" s="9">
         <v>50</v>
       </c>
-      <c r="H32" s="9">
+      <c r="I32" s="9">
         <v>70002940</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" s="6">
+      <c r="J32" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L32" s="6">
         <v>50001</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="M32" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="N32" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="M32" s="9">
+      <c r="O32" s="9">
         <v>5002</v>
       </c>
-      <c r="N32" s="12"/>
-      <c r="O32" s="18" t="s">
+      <c r="P32" s="12"/>
+      <c r="Q32" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="P32" s="18" t="s">
+      <c r="R32" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q32" s="6">
+      <c r="S32" s="6">
         <v>50001</v>
       </c>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6">
+      <c r="T32" s="6"/>
+      <c r="U32" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="6">
         <v>50002</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="G33" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G33" s="9">
+      <c r="H33" s="9">
         <v>52</v>
       </c>
-      <c r="H33" s="9">
+      <c r="I33" s="9">
         <v>70002950</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="6">
+      <c r="J33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L33" s="6">
         <v>50002</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="M33" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="N33" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="O33" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="N33" s="12"/>
-      <c r="O33" s="18" t="s">
+      <c r="P33" s="12"/>
+      <c r="Q33" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="P33" s="18" t="s">
+      <c r="R33" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="Q33" s="6">
+      <c r="S33" s="6">
         <v>50002</v>
       </c>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6">
+      <c r="T33" s="6"/>
+      <c r="U33" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6">
         <v>50003</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="G34" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G34" s="9">
+      <c r="H34" s="9">
         <v>52</v>
       </c>
-      <c r="H34" s="9">
+      <c r="I34" s="9">
         <v>70001910</v>
       </c>
-      <c r="I34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="6">
+      <c r="J34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L34" s="6">
         <v>50003</v>
       </c>
-      <c r="K34" s="14" t="s">
+      <c r="M34" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="N34" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="M34" s="16" t="s">
+      <c r="O34" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="N34" s="12"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="18" t="s">
+      <c r="P34" s="12"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q34" s="6">
+      <c r="S34" s="6">
         <v>50003</v>
       </c>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6">
+      <c r="T34" s="6"/>
+      <c r="U34" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6">
         <v>50004</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="G35" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G35" s="9">
+      <c r="H35" s="9">
         <v>54</v>
       </c>
-      <c r="H35" s="9">
+      <c r="I35" s="9">
         <v>70001920</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="6">
+      <c r="J35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L35" s="6">
         <v>50004</v>
       </c>
-      <c r="K35" s="14" t="s">
+      <c r="M35" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="N35" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="M35" s="16" t="s">
+      <c r="O35" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="N35" s="12"/>
-      <c r="O35" s="18" t="s">
+      <c r="P35" s="12"/>
+      <c r="Q35" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="P35" s="18" t="s">
+      <c r="R35" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q35" s="6">
+      <c r="S35" s="6">
         <v>50004</v>
       </c>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6">
+      <c r="T35" s="6"/>
+      <c r="U35" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="3:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="6">
         <v>50005</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="G36" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G36" s="9">
+      <c r="H36" s="9">
         <v>54</v>
       </c>
-      <c r="H36" s="9">
+      <c r="I36" s="9">
         <v>70001930</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="6">
+      <c r="J36" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L36" s="6">
         <v>50005</v>
       </c>
-      <c r="K36" s="14" t="s">
+      <c r="M36" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="L36" s="16" t="s">
+      <c r="N36" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="O36" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="N36" s="12"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="18" t="s">
+      <c r="P36" s="12"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q36" s="6">
+      <c r="S36" s="6">
         <v>50005</v>
       </c>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6">
+      <c r="T36" s="6"/>
+      <c r="U36" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="6">
         <v>50006</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="G37" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G37" s="9">
+      <c r="H37" s="9">
         <v>54</v>
       </c>
-      <c r="H37" s="9">
+      <c r="I37" s="9">
         <v>70001930</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="6">
+      <c r="J37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L37" s="6">
         <v>50006</v>
       </c>
-      <c r="K37" s="14" t="s">
+      <c r="M37" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="L37" s="9" t="s">
+      <c r="N37" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="O37" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="N37" s="12"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="18" t="s">
+      <c r="P37" s="12"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q37" s="6">
+      <c r="S37" s="6">
         <v>50006</v>
       </c>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6">
+      <c r="T37" s="6"/>
+      <c r="U37" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="6">
         <v>50007</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="G38" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G38" s="9">
+      <c r="H38" s="9">
         <v>56</v>
       </c>
-      <c r="H38" s="9">
+      <c r="I38" s="9">
         <v>70001930</v>
       </c>
-      <c r="I38" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="6">
+      <c r="J38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L38" s="6">
         <v>50007</v>
       </c>
-      <c r="K38" s="14" t="s">
+      <c r="M38" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="N38" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="M38" s="9">
+      <c r="O38" s="9">
         <v>5016</v>
       </c>
-      <c r="N38" s="12"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="18" t="s">
+      <c r="P38" s="12"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q38" s="6">
+      <c r="S38" s="6">
         <v>50007</v>
       </c>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6">
+      <c r="T38" s="6"/>
+      <c r="U38" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="6">
         <v>60001</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="G39" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G39" s="9">
+      <c r="H39" s="9">
         <v>60</v>
       </c>
-      <c r="H39" s="9">
+      <c r="I39" s="9">
         <v>70002940</v>
       </c>
-      <c r="I39" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="6">
+      <c r="J39" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L39" s="6">
         <v>60001</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="M39" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="N39" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="M39" s="9"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="18" t="s">
+      <c r="O39" s="9"/>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6">
+      <c r="S39" s="6"/>
+      <c r="T39" s="6">
         <v>61001</v>
       </c>
-      <c r="S39" s="6">
+      <c r="U39" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="6">
         <v>60002</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="G40" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G40" s="9">
+      <c r="H40" s="9">
         <v>62</v>
       </c>
-      <c r="H40" s="9">
+      <c r="I40" s="9">
         <v>70002940</v>
       </c>
-      <c r="I40" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J40" s="6">
+      <c r="J40" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L40" s="6">
         <v>60002</v>
       </c>
-      <c r="K40" s="14" t="s">
+      <c r="M40" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="N40" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M40" s="9"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="18" t="s">
+      <c r="O40" s="9"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6">
+      <c r="S40" s="6"/>
+      <c r="T40" s="6">
         <v>62001</v>
       </c>
-      <c r="S40" s="6">
+      <c r="U40" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="6">
         <v>60003</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="G41" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="G41" s="9">
+      <c r="H41" s="9">
         <v>65</v>
       </c>
-      <c r="H41" s="9">
+      <c r="I41" s="9">
         <v>70002940</v>
       </c>
-      <c r="I41" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J41" s="6">
+      <c r="J41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L41" s="6">
         <v>60003</v>
       </c>
-      <c r="K41" s="14" t="s">
+      <c r="M41" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="L41" s="9" t="s">
+      <c r="N41" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="M41" s="9"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="18" t="s">
+      <c r="O41" s="9"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6">
+      <c r="S41" s="6"/>
+      <c r="T41" s="6">
         <v>63001</v>
       </c>
-      <c r="S41" s="6">
+      <c r="U41" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
         <v>100001</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="G42" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G42" s="9">
+      <c r="H42" s="9">
         <v>1</v>
       </c>
-      <c r="H42" s="9">
+      <c r="I42" s="9">
         <v>0</v>
       </c>
-      <c r="I42" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J42" s="21">
+      <c r="J42" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L42" s="21">
         <v>2000010</v>
       </c>
-      <c r="K42" s="22" t="s">
+      <c r="M42" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="L42" s="9" t="s">
+      <c r="N42" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M42" s="9"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="18" t="s">
+      <c r="O42" s="9"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="13"/>
+      <c r="R42" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-    </row>
-    <row r="43" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+    </row>
+    <row r="43" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
         <v>100101</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="G43" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G43" s="9">
+      <c r="H43" s="9">
         <v>1</v>
       </c>
-      <c r="H43" s="9">
+      <c r="I43" s="9">
         <v>0</v>
       </c>
-      <c r="I43" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J43" s="6">
+      <c r="J43" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L43" s="6">
         <v>2000004</v>
       </c>
-      <c r="K43" s="14" t="s">
+      <c r="M43" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="L43" s="9" t="s">
+      <c r="N43" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M43" s="9"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="13" t="s">
+      <c r="O43" s="9"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="P43" s="18" t="s">
+      <c r="R43" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6">
+      <c r="S43" s="6"/>
+      <c r="T43" s="6">
         <v>10010101</v>
       </c>
-      <c r="S43" s="6"/>
-    </row>
-    <row r="44" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U43" s="6"/>
+    </row>
+    <row r="44" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
         <v>100201</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="G44" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G44" s="9">
+      <c r="H44" s="9">
         <v>18</v>
       </c>
-      <c r="H44" s="9">
+      <c r="I44" s="9">
         <v>0</v>
       </c>
-      <c r="I44" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J44" s="6">
+      <c r="J44" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L44" s="6">
         <v>2000004</v>
       </c>
-      <c r="K44" s="14" t="s">
+      <c r="M44" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="L44" s="9" t="s">
+      <c r="N44" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M44" s="9"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="13" t="s">
+      <c r="O44" s="9"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="P44" s="18" t="s">
+      <c r="R44" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6">
+      <c r="S44" s="6"/>
+      <c r="T44" s="6">
         <v>10020101</v>
       </c>
-      <c r="S44" s="6"/>
-    </row>
-    <row r="45" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U44" s="6"/>
+    </row>
+    <row r="45" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
         <v>100301</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="G45" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G45" s="9">
+      <c r="H45" s="9">
         <v>30</v>
       </c>
-      <c r="H45" s="9">
+      <c r="I45" s="9">
         <v>0</v>
       </c>
-      <c r="I45" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J45" s="6">
+      <c r="J45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L45" s="6">
         <v>2000004</v>
       </c>
-      <c r="K45" s="14" t="s">
+      <c r="M45" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="N45" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M45" s="9"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="13" t="s">
+      <c r="O45" s="9"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="P45" s="18" t="s">
+      <c r="R45" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6">
+      <c r="S45" s="6"/>
+      <c r="T45" s="6">
         <v>10030101</v>
       </c>
-      <c r="S45" s="6"/>
-    </row>
-    <row r="46" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U45" s="6"/>
+    </row>
+    <row r="46" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
         <v>100401</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="G46" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G46" s="9">
+      <c r="H46" s="9">
         <v>40</v>
       </c>
-      <c r="H46" s="9">
+      <c r="I46" s="9">
         <v>0</v>
       </c>
-      <c r="I46" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J46" s="6">
+      <c r="J46" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L46" s="6">
         <v>2000004</v>
       </c>
-      <c r="K46" s="14" t="s">
+      <c r="M46" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="L46" s="9" t="s">
+      <c r="N46" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M46" s="9"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="13" t="s">
+      <c r="O46" s="9"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="P46" s="18" t="s">
+      <c r="R46" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6">
+      <c r="S46" s="6"/>
+      <c r="T46" s="6">
         <v>10040101</v>
       </c>
-      <c r="S46" s="6"/>
-    </row>
-    <row r="47" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U46" s="6"/>
+    </row>
+    <row r="47" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
         <v>100501</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="G47" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G47" s="9">
+      <c r="H47" s="9">
         <v>50</v>
       </c>
-      <c r="H47" s="9">
+      <c r="I47" s="9">
         <v>0</v>
       </c>
-      <c r="I47" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J47" s="6">
+      <c r="J47" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L47" s="6">
         <v>2000004</v>
       </c>
-      <c r="K47" s="14" t="s">
+      <c r="M47" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="L47" s="9" t="s">
+      <c r="N47" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M47" s="9"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="13" t="s">
+      <c r="O47" s="9"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="P47" s="18" t="s">
+      <c r="R47" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6">
+      <c r="S47" s="6"/>
+      <c r="T47" s="6">
         <v>10050101</v>
       </c>
-      <c r="S47" s="6"/>
-    </row>
-    <row r="48" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U47" s="6"/>
+    </row>
+    <row r="48" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
         <v>100601</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="G48" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G48" s="9">
+      <c r="H48" s="9">
         <v>60</v>
       </c>
-      <c r="H48" s="9">
+      <c r="I48" s="9">
         <v>0</v>
       </c>
-      <c r="I48" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J48" s="6">
+      <c r="J48" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L48" s="6">
         <v>2000004</v>
       </c>
-      <c r="K48" s="14" t="s">
+      <c r="M48" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="L48" s="9" t="s">
+      <c r="N48" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M48" s="9"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13" t="s">
+      <c r="O48" s="9"/>
+      <c r="P48" s="12"/>
+      <c r="Q48" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="P48" s="18" t="s">
+      <c r="R48" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6">
+      <c r="S48" s="6"/>
+      <c r="T48" s="6">
         <v>10060101</v>
       </c>
-      <c r="S48" s="6"/>
+      <c r="U48" s="6"/>
     </row>
     <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ACE384-5EE1-44B4-AEC0-731BF8F36769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EA713E-9651-4904-A8BD-CA1E141E7009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -224,9 +224,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>矿洞一层</t>
-  </si>
-  <si>
     <t>15200,2930,-6764</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>1;148.26,28.78,-47.20;41001009;1@1;158.71,28.49,-40.11;41001009;1@1;167.23,29.01,-52.50;41001009;1@1;168.59,29.01,-70.45;41001009;1@1;158.29,29.01,-78.24;41001009;1@1;162.71,28.92,-61.39;41001009;1@1;169.35,29.01,-57.36;41001009;1@1;172.00,29.00,-36.39;41001009;1@1;159.52,28.77,-46.26;41001009;1@1;149.33,29.01,-56.47;41001009;1</t>
   </si>
   <si>
-    <t>绿林郊外</t>
-  </si>
-  <si>
     <t>15400,2910,-6336</t>
   </si>
   <si>
@@ -456,9 +450,6 @@
   </si>
   <si>
     <t>20003004</t>
-  </si>
-  <si>
-    <t>千针叶林</t>
   </si>
   <si>
     <t>14000,2905,-4277</t>
@@ -821,112 +812,13 @@
     <t>Greenwood Town</t>
   </si>
   <si>
-    <t>Level 1 of the Mine Shaft</t>
-  </si>
-  <si>
-    <t>Second floor of the mine</t>
-  </si>
-  <si>
-    <t>Outside the Forest</t>
-  </si>
-  <si>
-    <t>Deep in the Forest</t>
-  </si>
-  <si>
-    <t>Underground Cavern</t>
-  </si>
-  <si>
-    <t>The first floor of the stone tomb</t>
-  </si>
-  <si>
-    <t>Second Floor of the Tomb</t>
-  </si>
-  <si>
-    <t>Desert of Scorching Heat</t>
-  </si>
-  <si>
     <t>Oasis Path</t>
   </si>
   <si>
-    <t>Forget the Ruins</t>
-  </si>
-  <si>
-    <t>Floor 1 of the Dungeon</t>
-  </si>
-  <si>
-    <t>Second floor of the dungeon</t>
-  </si>
-  <si>
-    <t>Frozen Town</t>
-  </si>
-  <si>
-    <t>Frozen Forest</t>
-  </si>
-  <si>
-    <t>Frozen Fortress</t>
-  </si>
-  <si>
-    <t>Thousand-needle forest</t>
-  </si>
-  <si>
-    <t>Frozen Path</t>
-  </si>
-  <si>
-    <t>Frozen Demon穴</t>
-  </si>
-  <si>
-    <t>Dusk Town</t>
-  </si>
-  <si>
-    <t>The dusk outskirts</t>
-  </si>
-  <si>
-    <t>Dusk Forest</t>
-  </si>
-  <si>
-    <t>Dusk Mine Level 1</t>
-  </si>
-  <si>
-    <t>Second floor of the Twilight Mine</t>
-  </si>
-  <si>
     <t>Crack Stone Canyon</t>
   </si>
   <si>
-    <t>Hell Rift Valley</t>
-  </si>
-  <si>
     <t>Dark Town</t>
-  </si>
-  <si>
-    <t>Strange path</t>
-  </si>
-  <si>
-    <t>Corrosive Land</t>
-  </si>
-  <si>
-    <t>The first floor of the Dark Corridor</t>
-  </si>
-  <si>
-    <t>Dark Corridor Level 2</t>
-  </si>
-  <si>
-    <t>Dark Corridor, 3rd floor</t>
-  </si>
-  <si>
-    <t>Heart of Darkness</t>
-  </si>
-  <si>
-    <t>Skyland</t>
-  </si>
-  <si>
-    <t>Clear Sky Camp</t>
-  </si>
-  <si>
-    <t>Azure Sky Cavern</t>
-  </si>
-  <si>
-    <t>Mysterious Door - Joy</t>
   </si>
   <si>
     <t>Mysterious Door</t>
@@ -940,6 +832,121 @@
   </si>
   <si>
     <t>c</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>矿洞一层</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cave Level 1</t>
+  </si>
+  <si>
+    <t>Cave Level 2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿林郊外</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deep Green Woods</t>
+  </si>
+  <si>
+    <t>Underground Cave</t>
+  </si>
+  <si>
+    <t>Stone Tomb 1</t>
+  </si>
+  <si>
+    <t>Stone Tomb 2</t>
+  </si>
+  <si>
+    <t>Hot Desert</t>
+  </si>
+  <si>
+    <t>Forgotten Ruins</t>
+  </si>
+  <si>
+    <t>Dungeon 1</t>
+  </si>
+  <si>
+    <t>Dungeon 2</t>
+  </si>
+  <si>
+    <t>Ice Town</t>
+  </si>
+  <si>
+    <t>Ice Forest</t>
+  </si>
+  <si>
+    <t>Ice Fort</t>
+  </si>
+  <si>
+    <t>Ice Road</t>
+  </si>
+  <si>
+    <t>Ice Cave</t>
+  </si>
+  <si>
+    <t>Twilight Town</t>
+  </si>
+  <si>
+    <t>Twilight Outskirts</t>
+  </si>
+  <si>
+    <t>Twilight Forest</t>
+  </si>
+  <si>
+    <t>Twilight Mine 1</t>
+  </si>
+  <si>
+    <t>Twilight Mine 2</t>
+  </si>
+  <si>
+    <t>Hell Rift</t>
+  </si>
+  <si>
+    <t>Weird Path</t>
+  </si>
+  <si>
+    <t>Rotten Land</t>
+  </si>
+  <si>
+    <t>Dark Hall 1</t>
+  </si>
+  <si>
+    <t>Dark Hall 2</t>
+  </si>
+  <si>
+    <t>Dark Hall 3</t>
+  </si>
+  <si>
+    <t>Dark Heart</t>
+  </si>
+  <si>
+    <t>Blue Land</t>
+  </si>
+  <si>
+    <t>Blue Camp</t>
+  </si>
+  <si>
+    <t>Blue Cave</t>
+  </si>
+  <si>
+    <t>Green Outskirts</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>千针叶林</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pine Forest</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mysterious Door</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1354,9 +1361,9 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ChapterName"/>
-    <tableColumn id="7" xr3:uid="{BF7A43A1-7952-4509-B9DC-1DC3D8F11E4C}" name="ChapterName_EN" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{BF7A43A1-7952-4509-B9DC-1DC3D8F11E4C}" name="ChapterName_EN" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Music"/>
-    <tableColumn id="6" xr3:uid="{F00E6764-AD8C-429D-A124-148C7791A5DF}" name="MapType" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F00E6764-AD8C-429D-A124-148C7791A5DF}" name="MapType" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="EnterLv"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="BossIcon"/>
   </tableColumns>
@@ -1655,7 +1662,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="7" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="5" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.75" customWidth="1"/>
     <col min="8" max="9" width="17.25" customWidth="1"/>
     <col min="10" max="11" width="20.625" customWidth="1"/>
     <col min="12" max="13" width="17.25" customWidth="1"/>
@@ -1669,7 +1678,7 @@
     <row r="1" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K2" s="26" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1686,7 +1695,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>3</v>
@@ -1728,7 +1737,7 @@
         <v>12</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1739,13 +1748,13 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>15</v>
@@ -1757,7 +1766,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>18</v>
@@ -1787,7 +1796,7 @@
         <v>26</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1804,7 +1813,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>27</v>
@@ -1857,13 +1866,13 @@
         <v>31</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H6" s="7">
         <v>1</v>
@@ -1875,7 +1884,7 @@
         <v>33</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L6" s="6">
         <v>10001</v>
@@ -1911,16 +1920,16 @@
         <v>10002</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>40</v>
+        <v>234</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H7" s="10">
         <v>3</v>
@@ -1932,28 +1941,28 @@
         <v>33</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L7" s="6">
         <v>10002</v>
       </c>
       <c r="M7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="P7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="17" t="s">
+      <c r="Q7" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" s="18" t="s">
+      <c r="R7" s="18" t="s">
         <v>45</v>
-      </c>
-      <c r="R7" s="18" t="s">
-        <v>46</v>
       </c>
       <c r="S7" s="6">
         <v>10002</v>
@@ -1968,16 +1977,16 @@
         <v>10003</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>231</v>
+        <v>46</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H8" s="7">
         <v>5</v>
@@ -1989,28 +1998,28 @@
         <v>33</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L8" s="6">
         <v>10003</v>
       </c>
       <c r="M8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="O8" s="9">
         <v>1010</v>
       </c>
       <c r="P8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="R8" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="R8" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="S8" s="6">
         <v>10003</v>
@@ -2025,16 +2034,16 @@
         <v>10004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H9" s="7">
         <v>6</v>
@@ -2046,25 +2055,25 @@
         <v>33</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L9" s="6">
         <v>10004</v>
       </c>
       <c r="M9" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="P9" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="Q9" s="18" t="s">
         <v>56</v>
-      </c>
-      <c r="P9" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>58</v>
       </c>
       <c r="R9" s="18" t="s">
         <v>39</v>
@@ -2082,16 +2091,16 @@
         <v>10005</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H10" s="7">
         <v>6</v>
@@ -2103,25 +2112,25 @@
         <v>33</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L10" s="6">
         <v>10005</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O10" s="9">
         <v>1011</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q10" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R10" s="18" t="s">
         <v>39</v>
@@ -2139,16 +2148,16 @@
         <v>10006</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H11" s="7">
         <v>12</v>
@@ -2160,25 +2169,25 @@
         <v>33</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L11" s="6">
         <v>10006</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O11" s="9">
         <v>1012</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q11" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R11" s="18" t="s">
         <v>39</v>
@@ -2196,16 +2205,16 @@
         <v>10007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H12" s="7">
         <v>8</v>
@@ -2217,25 +2226,25 @@
         <v>33</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L12" s="6">
         <v>10007</v>
       </c>
       <c r="M12" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O12" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="P12" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="O12" s="19" t="s">
+      <c r="Q12" s="18" t="s">
         <v>71</v>
-      </c>
-      <c r="P12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q12" s="18" t="s">
-        <v>73</v>
       </c>
       <c r="R12" s="18" t="s">
         <v>39</v>
@@ -2253,16 +2262,16 @@
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H13" s="7">
         <v>8</v>
@@ -2274,25 +2283,25 @@
         <v>33</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L13" s="6">
         <v>10008</v>
       </c>
       <c r="M13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="P13" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="Q13" s="18" t="s">
         <v>77</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q13" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="R13" s="18" t="s">
         <v>39</v>
@@ -2310,16 +2319,16 @@
         <v>20001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H14" s="9">
         <v>15</v>
@@ -2331,28 +2340,28 @@
         <v>33</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L14" s="6">
         <v>20001</v>
       </c>
       <c r="M14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="O14" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="P14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="O14" s="16" t="s">
+      <c r="Q14" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="R14" s="18" t="s">
         <v>83</v>
-      </c>
-      <c r="P14" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q14" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>85</v>
       </c>
       <c r="S14" s="6">
         <v>20001</v>
@@ -2367,16 +2376,16 @@
         <v>20002</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H15" s="9">
         <v>20</v>
@@ -2388,25 +2397,25 @@
         <v>33</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L15" s="6">
         <v>20002</v>
       </c>
       <c r="M15" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="P15" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="16" t="s">
+      <c r="Q15" s="18" t="s">
         <v>89</v>
-      </c>
-      <c r="P15" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q15" s="18" t="s">
-        <v>91</v>
       </c>
       <c r="R15" s="18" t="s">
         <v>39</v>
@@ -2424,16 +2433,16 @@
         <v>20003</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H16" s="9">
         <v>23</v>
@@ -2445,28 +2454,28 @@
         <v>33</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L16" s="6">
         <v>20003</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O16" s="9">
         <v>2012</v>
       </c>
       <c r="P16" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q16" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="R16" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="Q16" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>97</v>
       </c>
       <c r="S16" s="6">
         <v>20003</v>
@@ -2481,16 +2490,16 @@
         <v>20004</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H17" s="9">
         <v>25</v>
@@ -2502,25 +2511,25 @@
         <v>33</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L17" s="6">
         <v>20004</v>
       </c>
       <c r="M17" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="O17" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="P17" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="O17" s="16" t="s">
+      <c r="Q17" s="18" t="s">
         <v>101</v>
-      </c>
-      <c r="P17" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q17" s="18" t="s">
-        <v>103</v>
       </c>
       <c r="R17" s="18" t="s">
         <v>39</v>
@@ -2538,16 +2547,16 @@
         <v>20005</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -2559,16 +2568,16 @@
         <v>33</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L18" s="6">
         <v>20005</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O18" s="9">
         <v>2014</v>
@@ -2591,16 +2600,16 @@
         <v>30001</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H19" s="9">
         <v>30</v>
@@ -2612,23 +2621,23 @@
         <v>33</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L19" s="6">
         <v>30001</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O19" s="9">
         <v>3002</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="R19" s="18" t="s">
         <v>39</v>
@@ -2646,16 +2655,16 @@
         <v>30002</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H20" s="9">
         <v>30</v>
@@ -2667,19 +2676,19 @@
         <v>33</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L20" s="6">
         <v>30002</v>
       </c>
       <c r="M20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="O20" s="16" t="s">
         <v>111</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="O20" s="16" t="s">
-        <v>113</v>
       </c>
       <c r="P20" s="12"/>
       <c r="Q20" s="13"/>
@@ -2699,16 +2708,16 @@
         <v>30003</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H21" s="9">
         <v>32</v>
@@ -2720,23 +2729,23 @@
         <v>33</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L21" s="6">
         <v>30003</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O21" s="9">
         <v>3012</v>
       </c>
       <c r="P21" s="12"/>
       <c r="Q21" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="R21" s="18" t="s">
         <v>39</v>
@@ -2754,16 +2763,16 @@
         <v>30004</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>118</v>
+        <v>267</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H22" s="9">
         <v>34</v>
@@ -2775,26 +2784,26 @@
         <v>33</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L22" s="6">
         <v>30004</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O22" s="16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P22" s="12"/>
       <c r="Q22" s="18" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="R22" s="18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="S22" s="6">
         <v>30004</v>
@@ -2809,16 +2818,16 @@
         <v>30005</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H23" s="9">
         <v>36</v>
@@ -2830,23 +2839,23 @@
         <v>33</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L23" s="6">
         <v>30005</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O23" s="16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P23" s="12"/>
       <c r="Q23" s="18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="R23" s="18" t="s">
         <v>39</v>
@@ -2864,16 +2873,16 @@
         <v>30006</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H24" s="9">
         <v>38</v>
@@ -2885,23 +2894,23 @@
         <v>33</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L24" s="6">
         <v>30006</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O24" s="9">
         <v>3015</v>
       </c>
       <c r="P24" s="12"/>
       <c r="Q24" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="R24" s="18" t="s">
         <v>39</v>
@@ -2919,16 +2928,16 @@
         <v>40001</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H25" s="9">
         <v>40</v>
@@ -2940,26 +2949,26 @@
         <v>33</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L25" s="6">
         <v>40001</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O25" s="16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P25" s="12"/>
       <c r="Q25" s="18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="R25" s="18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="S25" s="6">
         <v>40001</v>
@@ -2974,16 +2983,16 @@
         <v>40002</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H26" s="9">
         <v>40</v>
@@ -2995,19 +3004,19 @@
         <v>33</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L26" s="6">
         <v>40002</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O26" s="19" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="13"/>
@@ -3027,16 +3036,16 @@
         <v>40003</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H27" s="9">
         <v>42</v>
@@ -3048,23 +3057,23 @@
         <v>33</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L27" s="6">
         <v>40003</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O27" s="19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="R27" s="18" t="s">
         <v>39</v>
@@ -3082,16 +3091,16 @@
         <v>40004</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H28" s="9">
         <v>44</v>
@@ -3103,23 +3112,23 @@
         <v>33</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L28" s="6">
         <v>40004</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O28" s="19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="R28" s="18" t="s">
         <v>39</v>
@@ -3137,16 +3146,16 @@
         <v>40005</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H29" s="9">
         <v>44</v>
@@ -3158,16 +3167,16 @@
         <v>33</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L29" s="6">
         <v>40005</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O29" s="9">
         <v>4014</v>
@@ -3190,16 +3199,16 @@
         <v>40006</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H30" s="9">
         <v>46</v>
@@ -3211,23 +3220,23 @@
         <v>33</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L30" s="6">
         <v>40006</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O30" s="16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P30" s="12"/>
       <c r="Q30" s="18" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="R30" s="18" t="s">
         <v>39</v>
@@ -3245,16 +3254,16 @@
         <v>40007</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H31" s="9">
         <v>48</v>
@@ -3266,23 +3275,23 @@
         <v>33</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L31" s="6">
         <v>40007</v>
       </c>
       <c r="M31" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O31" s="9">
         <v>4015</v>
       </c>
       <c r="P31" s="12"/>
       <c r="Q31" s="18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="R31" s="18" t="s">
         <v>39</v>
@@ -3300,16 +3309,16 @@
         <v>50001</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H32" s="9">
         <v>50</v>
@@ -3321,23 +3330,23 @@
         <v>33</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L32" s="6">
         <v>50001</v>
       </c>
       <c r="M32" s="14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O32" s="9">
         <v>5002</v>
       </c>
       <c r="P32" s="12"/>
       <c r="Q32" s="18" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R32" s="18" t="s">
         <v>39</v>
@@ -3355,16 +3364,16 @@
         <v>50002</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H33" s="9">
         <v>52</v>
@@ -3376,26 +3385,26 @@
         <v>33</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L33" s="6">
         <v>50002</v>
       </c>
       <c r="M33" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O33" s="16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P33" s="12"/>
       <c r="Q33" s="18" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R33" s="18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="S33" s="6">
         <v>50002</v>
@@ -3410,16 +3419,16 @@
         <v>50003</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H34" s="9">
         <v>52</v>
@@ -3431,19 +3440,19 @@
         <v>33</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L34" s="6">
         <v>50003</v>
       </c>
       <c r="M34" s="14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O34" s="16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P34" s="12"/>
       <c r="Q34" s="13"/>
@@ -3463,16 +3472,16 @@
         <v>50004</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H35" s="9">
         <v>54</v>
@@ -3484,23 +3493,23 @@
         <v>33</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L35" s="6">
         <v>50004</v>
       </c>
       <c r="M35" s="14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O35" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P35" s="12"/>
       <c r="Q35" s="18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R35" s="18" t="s">
         <v>39</v>
@@ -3518,16 +3527,16 @@
         <v>50005</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H36" s="9">
         <v>54</v>
@@ -3539,19 +3548,19 @@
         <v>33</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L36" s="6">
         <v>50005</v>
       </c>
       <c r="M36" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O36" s="16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P36" s="12"/>
       <c r="Q36" s="13"/>
@@ -3571,16 +3580,16 @@
         <v>50006</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H37" s="9">
         <v>54</v>
@@ -3592,19 +3601,19 @@
         <v>33</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L37" s="6">
         <v>50006</v>
       </c>
       <c r="M37" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O37" s="16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P37" s="12"/>
       <c r="Q37" s="13"/>
@@ -3624,16 +3633,16 @@
         <v>50007</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H38" s="9">
         <v>56</v>
@@ -3645,16 +3654,16 @@
         <v>33</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L38" s="6">
         <v>50007</v>
       </c>
       <c r="M38" s="14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O38" s="9">
         <v>5016</v>
@@ -3677,16 +3686,16 @@
         <v>60001</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H39" s="9">
         <v>60</v>
@@ -3698,16 +3707,16 @@
         <v>33</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L39" s="6">
         <v>60001</v>
       </c>
       <c r="M39" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O39" s="9"/>
       <c r="P39" s="12"/>
@@ -3728,16 +3737,16 @@
         <v>60002</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H40" s="9">
         <v>62</v>
@@ -3749,16 +3758,16 @@
         <v>33</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L40" s="6">
         <v>60002</v>
       </c>
       <c r="M40" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O40" s="9"/>
       <c r="P40" s="12"/>
@@ -3779,16 +3788,16 @@
         <v>60003</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H41" s="9">
         <v>65</v>
@@ -3800,16 +3809,16 @@
         <v>33</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L41" s="6">
         <v>60003</v>
       </c>
       <c r="M41" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O41" s="9"/>
       <c r="P41" s="12"/>
@@ -3830,16 +3839,16 @@
         <v>100001</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H42" s="9">
         <v>1</v>
@@ -3851,16 +3860,16 @@
         <v>33</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L42" s="21">
         <v>2000010</v>
       </c>
       <c r="M42" s="22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="12"/>
@@ -3877,16 +3886,16 @@
         <v>100101</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H43" s="9">
         <v>1</v>
@@ -3898,21 +3907,21 @@
         <v>33</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L43" s="6">
         <v>2000004</v>
       </c>
       <c r="M43" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="12"/>
       <c r="Q43" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R43" s="18" t="s">
         <v>39</v>
@@ -3928,16 +3937,16 @@
         <v>100201</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H44" s="9">
         <v>18</v>
@@ -3949,21 +3958,21 @@
         <v>33</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L44" s="6">
         <v>2000004</v>
       </c>
       <c r="M44" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="12"/>
       <c r="Q44" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R44" s="18" t="s">
         <v>39</v>
@@ -3979,16 +3988,16 @@
         <v>100301</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H45" s="9">
         <v>30</v>
@@ -4000,21 +4009,21 @@
         <v>33</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L45" s="6">
         <v>2000004</v>
       </c>
       <c r="M45" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O45" s="9"/>
       <c r="P45" s="12"/>
       <c r="Q45" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R45" s="18" t="s">
         <v>39</v>
@@ -4030,16 +4039,16 @@
         <v>100401</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H46" s="9">
         <v>40</v>
@@ -4051,21 +4060,21 @@
         <v>33</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L46" s="6">
         <v>2000004</v>
       </c>
       <c r="M46" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O46" s="9"/>
       <c r="P46" s="12"/>
       <c r="Q46" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R46" s="18" t="s">
         <v>39</v>
@@ -4081,16 +4090,16 @@
         <v>100501</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H47" s="9">
         <v>50</v>
@@ -4102,21 +4111,21 @@
         <v>33</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L47" s="6">
         <v>2000004</v>
       </c>
       <c r="M47" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O47" s="9"/>
       <c r="P47" s="12"/>
       <c r="Q47" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R47" s="18" t="s">
         <v>39</v>
@@ -4132,16 +4141,16 @@
         <v>100601</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H48" s="9">
         <v>60</v>
@@ -4153,21 +4162,21 @@
         <v>33</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L48" s="6">
         <v>2000004</v>
       </c>
       <c r="M48" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O48" s="9"/>
       <c r="P48" s="12"/>
       <c r="Q48" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R48" s="18" t="s">
         <v>39</v>

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EA713E-9651-4904-A8BD-CA1E141E7009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BE221C-CAF4-44B5-9003-B2B34B57AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonProto" sheetId="1" r:id="rId1"/>
@@ -850,13 +850,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Deep Green Woods</t>
-  </si>
-  <si>
     <t>Underground Cave</t>
-  </si>
-  <si>
-    <t>Stone Tomb 1</t>
   </si>
   <si>
     <t>Stone Tomb 2</t>
@@ -947,6 +941,14 @@
   </si>
   <si>
     <t>Mysterious Door</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deep Green Woods</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone Tomb 1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2037,7 +2039,7 @@
         <v>237</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>193</v>
@@ -2094,7 +2096,7 @@
         <v>57</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>195</v>
@@ -2151,7 +2153,7 @@
         <v>61</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>194</v>
@@ -2208,7 +2210,7 @@
         <v>66</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>196</v>
@@ -2265,7 +2267,7 @@
         <v>72</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>196</v>
@@ -2322,7 +2324,7 @@
         <v>78</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>197</v>
@@ -2436,7 +2438,7 @@
         <v>90</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>197</v>
@@ -2493,7 +2495,7 @@
         <v>96</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>196</v>
@@ -2550,7 +2552,7 @@
         <v>102</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>196</v>
@@ -2603,7 +2605,7 @@
         <v>105</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>198</v>
@@ -2658,7 +2660,7 @@
         <v>108</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>198</v>
@@ -2711,7 +2713,7 @@
         <v>112</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>198</v>
@@ -2763,10 +2765,10 @@
         <v>30004</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>195</v>
@@ -2821,7 +2823,7 @@
         <v>121</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>195</v>
@@ -2876,7 +2878,7 @@
         <v>126</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>199</v>
@@ -2931,7 +2933,7 @@
         <v>130</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>198</v>
@@ -2986,7 +2988,7 @@
         <v>135</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>196</v>
@@ -3039,7 +3041,7 @@
         <v>139</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>196</v>
@@ -3094,7 +3096,7 @@
         <v>144</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>201</v>
@@ -3149,7 +3151,7 @@
         <v>149</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>201</v>
@@ -3257,7 +3259,7 @@
         <v>157</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>32</v>
@@ -3367,7 +3369,7 @@
         <v>164</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>194</v>
@@ -3422,7 +3424,7 @@
         <v>170</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>194</v>
@@ -3475,7 +3477,7 @@
         <v>174</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>200</v>
@@ -3530,7 +3532,7 @@
         <v>179</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>200</v>
@@ -3583,7 +3585,7 @@
         <v>183</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>200</v>
@@ -3636,7 +3638,7 @@
         <v>186</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>200</v>
@@ -3689,7 +3691,7 @@
         <v>189</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>195</v>
@@ -3740,7 +3742,7 @@
         <v>202</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>195</v>
@@ -3791,7 +3793,7 @@
         <v>217</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>195</v>
@@ -3842,7 +3844,7 @@
         <v>214</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>195</v>

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BE221C-CAF4-44B5-9003-B2B34B57AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6FE3F6-172C-4DA7-8601-9CCB7F01CDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,9 +206,6 @@
     <t>在人们眼中,这片区域有很深的危险,亲爱的冒险者,你准备好开始探险了嘛</t>
   </si>
   <si>
-    <t>720,127,-257</t>
-  </si>
-  <si>
     <t>13,50,-35,0,60</t>
   </si>
   <si>
@@ -949,6 +946,10 @@
   </si>
   <si>
     <t>Stone Tomb 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>720,31,-257</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1680,7 +1681,7 @@
     <row r="1" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K2" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1697,7 +1698,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>3</v>
@@ -1739,7 +1740,7 @@
         <v>12</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1750,13 +1751,13 @@
         <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>15</v>
@@ -1768,7 +1769,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>18</v>
@@ -1798,7 +1799,7 @@
         <v>26</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1815,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>27</v>
@@ -1868,13 +1869,13 @@
         <v>31</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H6" s="7">
         <v>1</v>
@@ -1886,28 +1887,28 @@
         <v>33</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L6" s="6">
         <v>10001</v>
       </c>
       <c r="M6" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="P6" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="17" t="s">
+      <c r="Q6" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="18" t="s">
+      <c r="R6" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="R6" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="S6" s="6">
         <v>10001</v>
@@ -1922,16 +1923,16 @@
         <v>10002</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>235</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H7" s="10">
         <v>3</v>
@@ -1943,28 +1944,28 @@
         <v>33</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L7" s="6">
         <v>10002</v>
       </c>
       <c r="M7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="P7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="P7" s="17" t="s">
+      <c r="Q7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="18" t="s">
+      <c r="R7" s="18" t="s">
         <v>44</v>
-      </c>
-      <c r="R7" s="18" t="s">
-        <v>45</v>
       </c>
       <c r="S7" s="6">
         <v>10002</v>
@@ -1979,16 +1980,16 @@
         <v>10003</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H8" s="7">
         <v>5</v>
@@ -2000,28 +2001,28 @@
         <v>33</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L8" s="6">
         <v>10003</v>
       </c>
       <c r="M8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>48</v>
       </c>
       <c r="O8" s="9">
         <v>1010</v>
       </c>
       <c r="P8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="R8" s="18" t="s">
         <v>50</v>
-      </c>
-      <c r="R8" s="18" t="s">
-        <v>51</v>
       </c>
       <c r="S8" s="6">
         <v>10003</v>
@@ -2036,16 +2037,16 @@
         <v>10004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H9" s="7">
         <v>6</v>
@@ -2057,28 +2058,28 @@
         <v>33</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L9" s="6">
         <v>10004</v>
       </c>
       <c r="M9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="P9" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="17" t="s">
+      <c r="Q9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q9" s="18" t="s">
-        <v>56</v>
-      </c>
       <c r="R9" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S9" s="6">
         <v>10004</v>
@@ -2093,16 +2094,16 @@
         <v>10005</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H10" s="7">
         <v>6</v>
@@ -2114,28 +2115,28 @@
         <v>33</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L10" s="6">
         <v>10005</v>
       </c>
       <c r="M10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="O10" s="9">
         <v>1011</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q10" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R10" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S10" s="6">
         <v>10005</v>
@@ -2150,16 +2151,16 @@
         <v>10006</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H11" s="7">
         <v>12</v>
@@ -2171,28 +2172,28 @@
         <v>33</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L11" s="6">
         <v>10006</v>
       </c>
       <c r="M11" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="O11" s="9">
         <v>1012</v>
       </c>
       <c r="P11" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="Q11" s="18" t="s">
-        <v>65</v>
-      </c>
       <c r="R11" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S11" s="6">
         <v>10006</v>
@@ -2207,16 +2208,16 @@
         <v>10007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H12" s="7">
         <v>8</v>
@@ -2228,28 +2229,28 @@
         <v>33</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L12" s="6">
         <v>10007</v>
       </c>
       <c r="M12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="O12" s="19" t="s">
+      <c r="P12" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="17" t="s">
+      <c r="Q12" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q12" s="18" t="s">
-        <v>71</v>
-      </c>
       <c r="R12" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S12" s="6">
         <v>10007</v>
@@ -2264,16 +2265,16 @@
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H13" s="7">
         <v>8</v>
@@ -2285,28 +2286,28 @@
         <v>33</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L13" s="6">
         <v>10008</v>
       </c>
       <c r="M13" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="P13" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="P13" s="17" t="s">
+      <c r="Q13" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q13" s="18" t="s">
-        <v>77</v>
-      </c>
       <c r="R13" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S13" s="6">
         <v>10008</v>
@@ -2321,16 +2322,16 @@
         <v>20001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H14" s="9">
         <v>15</v>
@@ -2342,28 +2343,28 @@
         <v>33</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L14" s="6">
         <v>20001</v>
       </c>
       <c r="M14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="O14" s="16" t="s">
+      <c r="P14" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="P14" s="17" t="s">
+      <c r="Q14" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="R14" s="18" t="s">
         <v>82</v>
-      </c>
-      <c r="Q14" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="S14" s="6">
         <v>20001</v>
@@ -2378,16 +2379,16 @@
         <v>20002</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H15" s="9">
         <v>20</v>
@@ -2399,28 +2400,28 @@
         <v>33</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L15" s="6">
         <v>20002</v>
       </c>
       <c r="M15" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="O15" s="16" t="s">
+      <c r="P15" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="P15" s="17" t="s">
+      <c r="Q15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q15" s="18" t="s">
-        <v>89</v>
-      </c>
       <c r="R15" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S15" s="6">
         <v>20002</v>
@@ -2435,16 +2436,16 @@
         <v>20003</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H16" s="9">
         <v>23</v>
@@ -2456,28 +2457,28 @@
         <v>33</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L16" s="6">
         <v>20003</v>
       </c>
       <c r="M16" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="N16" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="O16" s="9">
         <v>2012</v>
       </c>
       <c r="P16" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q16" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="Q16" s="18" t="s">
+      <c r="R16" s="18" t="s">
         <v>94</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>95</v>
       </c>
       <c r="S16" s="6">
         <v>20003</v>
@@ -2492,16 +2493,16 @@
         <v>20004</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H17" s="9">
         <v>25</v>
@@ -2513,28 +2514,28 @@
         <v>33</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L17" s="6">
         <v>20004</v>
       </c>
       <c r="M17" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="O17" s="16" t="s">
+      <c r="P17" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="P17" s="17" t="s">
+      <c r="Q17" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="Q17" s="18" t="s">
-        <v>101</v>
-      </c>
       <c r="R17" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S17" s="6">
         <v>20004</v>
@@ -2549,16 +2550,16 @@
         <v>20005</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -2570,16 +2571,16 @@
         <v>33</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L18" s="6">
         <v>20005</v>
       </c>
       <c r="M18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="O18" s="9">
         <v>2014</v>
@@ -2587,7 +2588,7 @@
       <c r="P18" s="12"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S18" s="6">
         <v>20005</v>
@@ -2602,16 +2603,16 @@
         <v>30001</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H19" s="9">
         <v>30</v>
@@ -2623,26 +2624,26 @@
         <v>33</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L19" s="6">
         <v>30001</v>
       </c>
       <c r="M19" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="O19" s="9">
         <v>3002</v>
       </c>
       <c r="P19" s="12"/>
       <c r="Q19" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R19" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S19" s="6">
         <v>30001</v>
@@ -2657,16 +2658,16 @@
         <v>30002</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H20" s="9">
         <v>30</v>
@@ -2678,24 +2679,24 @@
         <v>33</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L20" s="6">
         <v>30002</v>
       </c>
       <c r="M20" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="N20" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="O20" s="16" t="s">
-        <v>111</v>
       </c>
       <c r="P20" s="12"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S20" s="6">
         <v>30002</v>
@@ -2710,16 +2711,16 @@
         <v>30003</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H21" s="9">
         <v>32</v>
@@ -2731,26 +2732,26 @@
         <v>33</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L21" s="6">
         <v>30003</v>
       </c>
       <c r="M21" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="O21" s="9">
         <v>3012</v>
       </c>
       <c r="P21" s="12"/>
       <c r="Q21" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R21" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S21" s="6">
         <v>30003</v>
@@ -2765,16 +2766,16 @@
         <v>30004</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>266</v>
-      </c>
       <c r="F22" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H22" s="9">
         <v>34</v>
@@ -2786,26 +2787,26 @@
         <v>33</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L22" s="6">
         <v>30004</v>
       </c>
       <c r="M22" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="N22" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="16" t="s">
         <v>117</v>
-      </c>
-      <c r="O22" s="16" t="s">
-        <v>118</v>
       </c>
       <c r="P22" s="12"/>
       <c r="Q22" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="R22" s="18" t="s">
         <v>119</v>
-      </c>
-      <c r="R22" s="18" t="s">
-        <v>120</v>
       </c>
       <c r="S22" s="6">
         <v>30004</v>
@@ -2820,16 +2821,16 @@
         <v>30005</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H23" s="9">
         <v>36</v>
@@ -2841,26 +2842,26 @@
         <v>33</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L23" s="6">
         <v>30005</v>
       </c>
       <c r="M23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="O23" s="16" t="s">
         <v>123</v>
-      </c>
-      <c r="O23" s="16" t="s">
-        <v>124</v>
       </c>
       <c r="P23" s="12"/>
       <c r="Q23" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R23" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S23" s="6">
         <v>30005</v>
@@ -2875,16 +2876,16 @@
         <v>30006</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H24" s="9">
         <v>38</v>
@@ -2896,26 +2897,26 @@
         <v>33</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L24" s="6">
         <v>30006</v>
       </c>
       <c r="M24" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="O24" s="9">
         <v>3015</v>
       </c>
       <c r="P24" s="12"/>
       <c r="Q24" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R24" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S24" s="6">
         <v>30006</v>
@@ -2930,16 +2931,16 @@
         <v>40001</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H25" s="9">
         <v>40</v>
@@ -2951,26 +2952,26 @@
         <v>33</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L25" s="6">
         <v>40001</v>
       </c>
       <c r="M25" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="O25" s="16" t="s">
         <v>132</v>
-      </c>
-      <c r="O25" s="16" t="s">
-        <v>133</v>
       </c>
       <c r="P25" s="12"/>
       <c r="Q25" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R25" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S25" s="6">
         <v>40001</v>
@@ -2985,16 +2986,16 @@
         <v>40002</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H26" s="9">
         <v>40</v>
@@ -3006,24 +3007,24 @@
         <v>33</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L26" s="6">
         <v>40002</v>
       </c>
       <c r="M26" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="19" t="s">
         <v>137</v>
-      </c>
-      <c r="O26" s="19" t="s">
-        <v>138</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S26" s="6">
         <v>40002</v>
@@ -3038,16 +3039,16 @@
         <v>40003</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H27" s="9">
         <v>42</v>
@@ -3059,26 +3060,26 @@
         <v>33</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L27" s="6">
         <v>40003</v>
       </c>
       <c r="M27" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="O27" s="19" t="s">
         <v>141</v>
-      </c>
-      <c r="O27" s="19" t="s">
-        <v>142</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R27" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S27" s="6">
         <v>40003</v>
@@ -3093,16 +3094,16 @@
         <v>40004</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H28" s="9">
         <v>44</v>
@@ -3114,26 +3115,26 @@
         <v>33</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L28" s="6">
         <v>40004</v>
       </c>
       <c r="M28" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="O28" s="19" t="s">
         <v>146</v>
-      </c>
-      <c r="O28" s="19" t="s">
-        <v>147</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R28" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S28" s="6">
         <v>40004</v>
@@ -3148,16 +3149,16 @@
         <v>40005</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H29" s="9">
         <v>44</v>
@@ -3169,16 +3170,16 @@
         <v>33</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L29" s="6">
         <v>40005</v>
       </c>
       <c r="M29" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>151</v>
       </c>
       <c r="O29" s="9">
         <v>4014</v>
@@ -3186,7 +3187,7 @@
       <c r="P29" s="12"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S29" s="6">
         <v>40005</v>
@@ -3201,16 +3202,16 @@
         <v>40006</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H30" s="9">
         <v>46</v>
@@ -3222,26 +3223,26 @@
         <v>33</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L30" s="6">
         <v>40006</v>
       </c>
       <c r="M30" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="O30" s="16" t="s">
         <v>154</v>
-      </c>
-      <c r="O30" s="16" t="s">
-        <v>155</v>
       </c>
       <c r="P30" s="12"/>
       <c r="Q30" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R30" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S30" s="6">
         <v>40006</v>
@@ -3256,16 +3257,16 @@
         <v>40007</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H31" s="9">
         <v>48</v>
@@ -3277,26 +3278,26 @@
         <v>33</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L31" s="6">
         <v>40007</v>
       </c>
       <c r="M31" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="O31" s="9">
         <v>4015</v>
       </c>
       <c r="P31" s="12"/>
       <c r="Q31" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R31" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S31" s="6">
         <v>40007</v>
@@ -3311,16 +3312,16 @@
         <v>50001</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H32" s="9">
         <v>50</v>
@@ -3332,26 +3333,26 @@
         <v>33</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L32" s="6">
         <v>50001</v>
       </c>
       <c r="M32" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="N32" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>163</v>
       </c>
       <c r="O32" s="9">
         <v>5002</v>
       </c>
       <c r="P32" s="12"/>
       <c r="Q32" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R32" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S32" s="6">
         <v>50001</v>
@@ -3366,16 +3367,16 @@
         <v>50002</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H33" s="9">
         <v>52</v>
@@ -3387,26 +3388,26 @@
         <v>33</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L33" s="6">
         <v>50002</v>
       </c>
       <c r="M33" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="N33" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="O33" s="16" t="s">
         <v>166</v>
-      </c>
-      <c r="O33" s="16" t="s">
-        <v>167</v>
       </c>
       <c r="P33" s="12"/>
       <c r="Q33" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="R33" s="18" t="s">
         <v>168</v>
-      </c>
-      <c r="R33" s="18" t="s">
-        <v>169</v>
       </c>
       <c r="S33" s="6">
         <v>50002</v>
@@ -3421,16 +3422,16 @@
         <v>50003</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H34" s="9">
         <v>52</v>
@@ -3442,24 +3443,24 @@
         <v>33</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L34" s="6">
         <v>50003</v>
       </c>
       <c r="M34" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="N34" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="O34" s="16" t="s">
         <v>172</v>
-      </c>
-      <c r="O34" s="16" t="s">
-        <v>173</v>
       </c>
       <c r="P34" s="12"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S34" s="6">
         <v>50003</v>
@@ -3474,16 +3475,16 @@
         <v>50004</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H35" s="9">
         <v>54</v>
@@ -3495,26 +3496,26 @@
         <v>33</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L35" s="6">
         <v>50004</v>
       </c>
       <c r="M35" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="N35" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="O35" s="16" t="s">
-        <v>177</v>
       </c>
       <c r="P35" s="12"/>
       <c r="Q35" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R35" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S35" s="6">
         <v>50004</v>
@@ -3529,16 +3530,16 @@
         <v>50005</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H36" s="9">
         <v>54</v>
@@ -3550,24 +3551,24 @@
         <v>33</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L36" s="6">
         <v>50005</v>
       </c>
       <c r="M36" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="N36" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="N36" s="16" t="s">
+      <c r="O36" s="16" t="s">
         <v>181</v>
-      </c>
-      <c r="O36" s="16" t="s">
-        <v>182</v>
       </c>
       <c r="P36" s="12"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S36" s="6">
         <v>50005</v>
@@ -3582,16 +3583,16 @@
         <v>50006</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H37" s="9">
         <v>54</v>
@@ -3603,24 +3604,24 @@
         <v>33</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L37" s="6">
         <v>50006</v>
       </c>
       <c r="M37" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="N37" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="N37" s="9" t="s">
-        <v>185</v>
-      </c>
       <c r="O37" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P37" s="12"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S37" s="6">
         <v>50006</v>
@@ -3635,16 +3636,16 @@
         <v>50007</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H38" s="9">
         <v>56</v>
@@ -3656,16 +3657,16 @@
         <v>33</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L38" s="6">
         <v>50007</v>
       </c>
       <c r="M38" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="N38" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="N38" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="O38" s="9">
         <v>5016</v>
@@ -3673,7 +3674,7 @@
       <c r="P38" s="12"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S38" s="6">
         <v>50007</v>
@@ -3688,16 +3689,16 @@
         <v>60001</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H39" s="9">
         <v>60</v>
@@ -3709,22 +3710,22 @@
         <v>33</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L39" s="6">
         <v>60001</v>
       </c>
       <c r="M39" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="N39" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="O39" s="9"/>
       <c r="P39" s="12"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S39" s="6"/>
       <c r="T39" s="6">
@@ -3739,16 +3740,16 @@
         <v>60002</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H40" s="9">
         <v>62</v>
@@ -3760,22 +3761,22 @@
         <v>33</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L40" s="6">
         <v>60002</v>
       </c>
       <c r="M40" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="N40" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="O40" s="9"/>
       <c r="P40" s="12"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S40" s="6"/>
       <c r="T40" s="6">
@@ -3790,16 +3791,16 @@
         <v>60003</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H41" s="9">
         <v>65</v>
@@ -3811,22 +3812,22 @@
         <v>33</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L41" s="6">
         <v>60003</v>
       </c>
       <c r="M41" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O41" s="9"/>
       <c r="P41" s="12"/>
       <c r="Q41" s="13"/>
       <c r="R41" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S41" s="6"/>
       <c r="T41" s="6">
@@ -3841,16 +3842,16 @@
         <v>100001</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H42" s="9">
         <v>1</v>
@@ -3862,22 +3863,22 @@
         <v>33</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L42" s="21">
         <v>2000010</v>
       </c>
       <c r="M42" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="12"/>
       <c r="Q42" s="13"/>
       <c r="R42" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
@@ -3888,16 +3889,16 @@
         <v>100101</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H43" s="9">
         <v>1</v>
@@ -3909,24 +3910,24 @@
         <v>33</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L43" s="6">
         <v>2000004</v>
       </c>
       <c r="M43" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="12"/>
       <c r="Q43" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R43" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6">
@@ -3939,16 +3940,16 @@
         <v>100201</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H44" s="9">
         <v>18</v>
@@ -3960,24 +3961,24 @@
         <v>33</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L44" s="6">
         <v>2000004</v>
       </c>
       <c r="M44" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="12"/>
       <c r="Q44" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R44" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S44" s="6"/>
       <c r="T44" s="6">
@@ -3990,16 +3991,16 @@
         <v>100301</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H45" s="9">
         <v>30</v>
@@ -4011,24 +4012,24 @@
         <v>33</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L45" s="6">
         <v>2000004</v>
       </c>
       <c r="M45" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O45" s="9"/>
       <c r="P45" s="12"/>
       <c r="Q45" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R45" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S45" s="6"/>
       <c r="T45" s="6">
@@ -4041,16 +4042,16 @@
         <v>100401</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H46" s="9">
         <v>40</v>
@@ -4062,24 +4063,24 @@
         <v>33</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L46" s="6">
         <v>2000004</v>
       </c>
       <c r="M46" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O46" s="9"/>
       <c r="P46" s="12"/>
       <c r="Q46" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R46" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S46" s="6"/>
       <c r="T46" s="6">
@@ -4092,16 +4093,16 @@
         <v>100501</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H47" s="9">
         <v>50</v>
@@ -4113,24 +4114,24 @@
         <v>33</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L47" s="6">
         <v>2000004</v>
       </c>
       <c r="M47" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O47" s="9"/>
       <c r="P47" s="12"/>
       <c r="Q47" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R47" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S47" s="6"/>
       <c r="T47" s="6">
@@ -4143,16 +4144,16 @@
         <v>100601</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H48" s="9">
         <v>60</v>
@@ -4164,24 +4165,24 @@
         <v>33</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L48" s="6">
         <v>2000004</v>
       </c>
       <c r="M48" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O48" s="9"/>
       <c r="P48" s="12"/>
       <c r="Q48" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R48" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S48" s="6"/>
       <c r="T48" s="6">

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6FE3F6-172C-4DA7-8601-9CCB7F01CDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D846C459-084A-4A9C-8C7D-E5296AC99FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="293">
   <si>
     <t>Id</t>
   </si>
@@ -950,6 +950,81 @@
   </si>
   <si>
     <t>720,31,-257</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoadingImg</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
+    <t>10005</t>
+  </si>
+  <si>
+    <t>10006</t>
+  </si>
+  <si>
+    <t>10008</t>
+  </si>
+  <si>
+    <t>20002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>20004</t>
+  </si>
+  <si>
+    <t>30001</t>
+  </si>
+  <si>
+    <t>30003</t>
+  </si>
+  <si>
+    <t>30004</t>
+  </si>
+  <si>
+    <t>30005</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t>40001</t>
+  </si>
+  <si>
+    <t>40002</t>
+  </si>
+  <si>
+    <t>40003</t>
+  </si>
+  <si>
+    <t>20003</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>30002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>40006</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loading图片</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1661,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:U53"/>
+  <dimension ref="C1:V53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="7.5" customWidth="1"/>
@@ -1676,15 +1751,16 @@
     <col min="17" max="17" width="87" customWidth="1"/>
     <col min="18" max="18" width="63.25" customWidth="1"/>
     <col min="19" max="21" width="23.125" customWidth="1"/>
+    <col min="22" max="22" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K2" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1742,8 +1818,11 @@
       <c r="U3" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="4" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V3" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="4" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1801,8 +1880,11 @@
       <c r="U4" s="4" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="5" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V4" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="4" t="s">
         <v>27</v>
       </c>
@@ -1860,8 +1942,11 @@
       <c r="U5" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V5" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>10001</v>
       </c>
@@ -1917,8 +2002,11 @@
       <c r="U6" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V6" s="18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="6">
         <v>10002</v>
       </c>
@@ -1974,8 +2062,11 @@
       <c r="U7" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V7" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>10003</v>
       </c>
@@ -2031,8 +2122,11 @@
       <c r="U8" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V8" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="6">
         <v>10004</v>
       </c>
@@ -2088,8 +2182,11 @@
       <c r="U9" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V9" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="6">
         <v>10005</v>
       </c>
@@ -2145,8 +2242,11 @@
       <c r="U10" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V10" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="6">
         <v>10006</v>
       </c>
@@ -2202,8 +2302,11 @@
       <c r="U11" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V11" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="6">
         <v>10007</v>
       </c>
@@ -2259,8 +2362,11 @@
       <c r="U12" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V12" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="6">
         <v>10008</v>
       </c>
@@ -2316,8 +2422,11 @@
       <c r="U13" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V13" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
         <v>20001</v>
       </c>
@@ -2373,8 +2482,11 @@
       <c r="U14" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V14" s="6">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="15" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
         <v>20002</v>
       </c>
@@ -2430,8 +2542,11 @@
       <c r="U15" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V15" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
         <v>20003</v>
       </c>
@@ -2487,8 +2602,11 @@
       <c r="U16" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V16" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
         <v>20004</v>
       </c>
@@ -2544,8 +2662,11 @@
       <c r="U17" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V17" s="18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
         <v>20005</v>
       </c>
@@ -2597,8 +2718,11 @@
       <c r="U18" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V18" s="18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
         <v>30001</v>
       </c>
@@ -2652,8 +2776,11 @@
       <c r="U19" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V19" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
         <v>30002</v>
       </c>
@@ -2705,8 +2832,11 @@
       <c r="U20" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V20" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="6">
         <v>30003</v>
       </c>
@@ -2760,8 +2890,11 @@
       <c r="U21" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V21" s="18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="6">
         <v>30004</v>
       </c>
@@ -2815,8 +2948,11 @@
       <c r="U22" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V22" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="6">
         <v>30005</v>
       </c>
@@ -2870,8 +3006,11 @@
       <c r="U23" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V23" s="18" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="6">
         <v>30006</v>
       </c>
@@ -2925,8 +3064,11 @@
       <c r="U24" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V24" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="6">
         <v>40001</v>
       </c>
@@ -2980,8 +3122,11 @@
       <c r="U25" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V25" s="18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="6">
         <v>40002</v>
       </c>
@@ -3033,8 +3178,11 @@
       <c r="U26" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V26" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="6">
         <v>40003</v>
       </c>
@@ -3088,8 +3236,11 @@
       <c r="U27" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V27" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="6">
         <v>40004</v>
       </c>
@@ -3143,8 +3294,11 @@
       <c r="U28" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V28" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="6">
         <v>40005</v>
       </c>
@@ -3196,8 +3350,11 @@
       <c r="U29" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V29" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="6">
         <v>40006</v>
       </c>
@@ -3251,8 +3408,11 @@
       <c r="U30" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V30" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="6">
         <v>40007</v>
       </c>
@@ -3306,8 +3466,11 @@
       <c r="U31" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V31" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="6">
         <v>50001</v>
       </c>
@@ -3361,8 +3524,11 @@
       <c r="U32" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V32" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="6">
         <v>50002</v>
       </c>
@@ -3416,8 +3582,11 @@
       <c r="U33" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V33" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="34" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6">
         <v>50003</v>
       </c>
@@ -3469,8 +3638,11 @@
       <c r="U34" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V34" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="35" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6">
         <v>50004</v>
       </c>
@@ -3524,8 +3696,11 @@
       <c r="U35" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="3:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V35" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="3:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="6">
         <v>50005</v>
       </c>
@@ -3577,8 +3752,11 @@
       <c r="U36" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V36" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="6">
         <v>50006</v>
       </c>
@@ -3630,8 +3808,11 @@
       <c r="U37" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V37" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="6">
         <v>50007</v>
       </c>
@@ -3683,8 +3864,11 @@
       <c r="U38" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V38" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="6">
         <v>60001</v>
       </c>
@@ -3734,8 +3918,11 @@
       <c r="U39" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V39" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="40" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="6">
         <v>60002</v>
       </c>
@@ -3785,8 +3972,11 @@
       <c r="U40" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V40" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="6">
         <v>60003</v>
       </c>
@@ -3836,8 +4026,11 @@
       <c r="U41" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V41" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="42" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
         <v>100001</v>
       </c>
@@ -3883,8 +4076,11 @@
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
       <c r="U42" s="6"/>
-    </row>
-    <row r="43" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V42" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
         <v>100101</v>
       </c>
@@ -3934,8 +4130,11 @@
         <v>10010101</v>
       </c>
       <c r="U43" s="6"/>
-    </row>
-    <row r="44" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V43" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
         <v>100201</v>
       </c>
@@ -3985,8 +4184,11 @@
         <v>10020101</v>
       </c>
       <c r="U44" s="6"/>
-    </row>
-    <row r="45" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V44" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
         <v>100301</v>
       </c>
@@ -4036,8 +4238,11 @@
         <v>10030101</v>
       </c>
       <c r="U45" s="6"/>
-    </row>
-    <row r="46" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V45" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
         <v>100401</v>
       </c>
@@ -4087,8 +4292,11 @@
         <v>10040101</v>
       </c>
       <c r="U46" s="6"/>
-    </row>
-    <row r="47" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V46" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="47" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
         <v>100501</v>
       </c>
@@ -4138,8 +4346,11 @@
         <v>10050101</v>
       </c>
       <c r="U47" s="6"/>
-    </row>
-    <row r="48" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V47" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="48" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
         <v>100601</v>
       </c>
@@ -4189,6 +4400,9 @@
         <v>10060101</v>
       </c>
       <c r="U48" s="6"/>
+      <c r="V48" s="18" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D846C459-084A-4A9C-8C7D-E5296AC99FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98EB65F-4741-4E9E-AFEA-AC38DBD33C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="296">
   <si>
     <t>Id</t>
   </si>
@@ -1025,6 +1025,17 @@
   </si>
   <si>
     <t>Loading图片</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣像之域</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Statue Domain</t>
+  </si>
+  <si>
+    <t>30790,1230,-6900</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1736,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:V53"/>
+  <dimension ref="C1:V54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="7.5" customWidth="1"/>
@@ -4032,25 +4043,25 @@
     </row>
     <row r="42" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
-        <v>100001</v>
+        <v>60004</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>213</v>
+        <v>293</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="G42" s="8" t="s">
-        <v>211</v>
+      <c r="G42" s="20" t="s">
+        <v>210</v>
       </c>
       <c r="H42" s="9">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="I42" s="9">
-        <v>0</v>
+        <v>70002940</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>33</v>
@@ -4058,14 +4069,14 @@
       <c r="K42" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="L42" s="21">
-        <v>2000010</v>
-      </c>
-      <c r="M42" s="22" t="s">
-        <v>212</v>
+      <c r="L42" s="6">
+        <v>60004</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="12"/>
@@ -4074,27 +4085,31 @@
         <v>38</v>
       </c>
       <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
+      <c r="T42" s="6">
+        <v>64001</v>
+      </c>
+      <c r="U42" s="6">
+        <v>6</v>
+      </c>
       <c r="V42" s="18" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
-        <v>100101</v>
+        <v>100001</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>194</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H43" s="9">
         <v>1</v>
@@ -4108,27 +4123,23 @@
       <c r="K43" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="L43" s="6">
-        <v>2000004</v>
-      </c>
-      <c r="M43" s="14" t="s">
-        <v>206</v>
+      <c r="L43" s="21">
+        <v>2000010</v>
+      </c>
+      <c r="M43" s="22" t="s">
+        <v>212</v>
       </c>
       <c r="N43" s="9" t="s">
         <v>203</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="12"/>
-      <c r="Q43" s="13" t="s">
-        <v>219</v>
-      </c>
+      <c r="Q43" s="13"/>
       <c r="R43" s="18" t="s">
         <v>38</v>
       </c>
       <c r="S43" s="6"/>
-      <c r="T43" s="6">
-        <v>10010101</v>
-      </c>
+      <c r="T43" s="6"/>
       <c r="U43" s="6"/>
       <c r="V43" s="18" t="s">
         <v>291</v>
@@ -4136,7 +4147,7 @@
     </row>
     <row r="44" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
-        <v>100201</v>
+        <v>100101</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>205</v>
@@ -4151,7 +4162,7 @@
         <v>210</v>
       </c>
       <c r="H44" s="9">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I44" s="9">
         <v>0</v>
@@ -4181,7 +4192,7 @@
       </c>
       <c r="S44" s="6"/>
       <c r="T44" s="6">
-        <v>10020101</v>
+        <v>10010101</v>
       </c>
       <c r="U44" s="6"/>
       <c r="V44" s="18" t="s">
@@ -4190,7 +4201,7 @@
     </row>
     <row r="45" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
-        <v>100301</v>
+        <v>100201</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>205</v>
@@ -4205,7 +4216,7 @@
         <v>210</v>
       </c>
       <c r="H45" s="9">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I45" s="9">
         <v>0</v>
@@ -4235,7 +4246,7 @@
       </c>
       <c r="S45" s="6"/>
       <c r="T45" s="6">
-        <v>10030101</v>
+        <v>10020101</v>
       </c>
       <c r="U45" s="6"/>
       <c r="V45" s="18" t="s">
@@ -4244,7 +4255,7 @@
     </row>
     <row r="46" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
-        <v>100401</v>
+        <v>100301</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>205</v>
@@ -4259,7 +4270,7 @@
         <v>210</v>
       </c>
       <c r="H46" s="9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I46" s="9">
         <v>0</v>
@@ -4289,7 +4300,7 @@
       </c>
       <c r="S46" s="6"/>
       <c r="T46" s="6">
-        <v>10040101</v>
+        <v>10030101</v>
       </c>
       <c r="U46" s="6"/>
       <c r="V46" s="18" t="s">
@@ -4298,7 +4309,7 @@
     </row>
     <row r="47" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
-        <v>100501</v>
+        <v>100401</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>205</v>
@@ -4313,7 +4324,7 @@
         <v>210</v>
       </c>
       <c r="H47" s="9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I47" s="9">
         <v>0</v>
@@ -4343,7 +4354,7 @@
       </c>
       <c r="S47" s="6"/>
       <c r="T47" s="6">
-        <v>10050101</v>
+        <v>10040101</v>
       </c>
       <c r="U47" s="6"/>
       <c r="V47" s="18" t="s">
@@ -4352,7 +4363,7 @@
     </row>
     <row r="48" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
-        <v>100601</v>
+        <v>100501</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>205</v>
@@ -4367,7 +4378,7 @@
         <v>210</v>
       </c>
       <c r="H48" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I48" s="9">
         <v>0</v>
@@ -4397,25 +4408,79 @@
       </c>
       <c r="S48" s="6"/>
       <c r="T48" s="6">
-        <v>10060101</v>
+        <v>10050101</v>
       </c>
       <c r="U48" s="6"/>
       <c r="V48" s="18" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C49" s="6">
+        <v>100601</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="H49" s="9">
+        <v>60</v>
+      </c>
+      <c r="I49" s="9">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="L49" s="6">
+        <v>2000004</v>
+      </c>
+      <c r="M49" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="O49" s="9"/>
+      <c r="P49" s="12"/>
+      <c r="Q49" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="R49" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="S49" s="6"/>
+      <c r="T49" s="6">
+        <v>10060101</v>
+      </c>
+      <c r="U49" s="6"/>
+      <c r="V49" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98EB65F-4741-4E9E-AFEA-AC38DBD33C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B1DE8F-9773-4DAF-9B3D-6252DCADCC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="297">
   <si>
     <t>Id</t>
   </si>
@@ -1035,7 +1035,11 @@
     <t>Statue Domain</t>
   </si>
   <si>
-    <t>30790,1230,-6900</t>
+    <t>30790,0,-6900</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>240,120,-70,0,70</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -4058,7 +4062,7 @@
         <v>210</v>
       </c>
       <c r="H42" s="9">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I42" s="9">
         <v>70002940</v>
@@ -4076,7 +4080,7 @@
         <v>295</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>217</v>
+        <v>296</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="12"/>

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B1DE8F-9773-4DAF-9B3D-6252DCADCC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2100563-0624-44F6-AC10-3AD106BB33AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/DungeonConfig.xlsx
+++ b/Excel/DungeonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2100563-0624-44F6-AC10-3AD106BB33AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE15762-939F-411F-A7FA-4241F4F9E8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1035,11 +1035,11 @@
     <t>Statue Domain</t>
   </si>
   <si>
-    <t>30790,0,-6900</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>240,120,-70,0,70</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>30790,1049,-6900</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -4077,10 +4077,10 @@
         <v>60004</v>
       </c>
       <c r="M42" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="N42" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="12"/>
